--- a/docs/ophir/ophir-maliyet-talebi.xlsx
+++ b/docs/ophir/ophir-maliyet-talebi.xlsx
@@ -81,7 +81,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -106,11 +106,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -140,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -160,10 +155,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -764,21 +755,17 @@
           <t>band</t>
         </is>
       </c>
-      <c r="F3" s="11" t="n">
-        <v>1.5</v>
+      <c r="F3" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I3" s="11" t="n">
+      <c r="I3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="12" t="inlineStr">
-        <is>
-          <t>GENISLIGI TEYIT ET</t>
-        </is>
-      </c>
+      <c r="J3" s="5" t="inlineStr"/>
       <c r="K3" s="5" t="inlineStr">
         <is>
           <t>tekil/aksan tas</t>
@@ -798,7 +785,7 @@
         <v/>
       </c>
       <c r="S3" s="10" t="n">
-        <v>1.48</v>
+        <v>0.99</v>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
@@ -1130,21 +1117,17 @@
           <t>band</t>
         </is>
       </c>
-      <c r="F9" s="11" t="n">
-        <v>1.5</v>
+      <c r="F9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="I9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="J9" s="12" t="inlineStr">
-        <is>
-          <t>GENISLIGI TEYIT ET</t>
-        </is>
-      </c>
+      <c r="J9" s="5" t="inlineStr"/>
       <c r="K9" s="5" t="inlineStr">
         <is>
           <t>yok / none</t>
@@ -1164,7 +1147,7 @@
         <v/>
       </c>
       <c r="S9" s="10" t="n">
-        <v>1.48</v>
+        <v>5.93</v>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
@@ -1254,21 +1237,17 @@
           <t>band</t>
         </is>
       </c>
-      <c r="F11" s="11" t="n">
-        <v>1.5</v>
+      <c r="F11" s="3" t="n">
+        <v>3.1</v>
       </c>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="J11" s="12" t="inlineStr">
-        <is>
-          <t>GENISLIGI TEYIT ET</t>
-        </is>
-      </c>
+      <c r="J11" s="5" t="inlineStr"/>
       <c r="K11" s="5" t="inlineStr">
         <is>
           <t>tam eternity</t>
@@ -1288,7 +1267,7 @@
         <v/>
       </c>
       <c r="S11" s="10" t="n">
-        <v>1.48</v>
+        <v>3.06</v>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
@@ -1918,21 +1897,17 @@
           <t>band</t>
         </is>
       </c>
-      <c r="F22" s="11" t="n">
-        <v>1.6</v>
+      <c r="F22" s="3" t="n">
+        <v>3.6</v>
       </c>
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="I22" s="11" t="n">
+      <c r="I22" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="J22" s="12" t="inlineStr">
-        <is>
-          <t>GENISLIGI TEYIT ET</t>
-        </is>
-      </c>
+      <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="5" t="inlineStr">
         <is>
           <t>yok / none</t>
@@ -1952,7 +1927,7 @@
         <v/>
       </c>
       <c r="S22" s="10" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
@@ -3182,21 +3157,17 @@
           <t>band</t>
         </is>
       </c>
-      <c r="F43" s="11" t="n">
-        <v>1.5</v>
+      <c r="F43" s="3" t="n">
+        <v>2.5</v>
       </c>
       <c r="G43" s="3" t="n"/>
       <c r="H43" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I43" s="11" t="n">
+      <c r="I43" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J43" s="12" t="inlineStr">
-        <is>
-          <t>GENISLIGI TEYIT ET</t>
-        </is>
-      </c>
+      <c r="J43" s="5" t="inlineStr"/>
       <c r="K43" s="5" t="inlineStr">
         <is>
           <t>yarim eternity</t>
@@ -3216,7 +3187,7 @@
         <v/>
       </c>
       <c r="S43" s="10" t="n">
-        <v>1.48</v>
+        <v>2.47</v>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
@@ -3486,21 +3457,17 @@
           <t>band</t>
         </is>
       </c>
-      <c r="F48" s="11" t="n">
+      <c r="F48" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="G48" s="3" t="n"/>
       <c r="H48" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I48" s="11" t="n">
+      <c r="I48" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="J48" s="12" t="inlineStr">
-        <is>
-          <t>GENISLIGI TEYIT ET</t>
-        </is>
-      </c>
+      <c r="J48" s="5" t="inlineStr"/>
       <c r="K48" s="5" t="inlineStr">
         <is>
           <t>tekil/aksan tas</t>
@@ -4090,21 +4057,17 @@
           <t>band</t>
         </is>
       </c>
-      <c r="F58" s="11" t="n">
-        <v>1.5</v>
+      <c r="F58" s="3" t="n">
+        <v>3.1</v>
       </c>
       <c r="G58" s="3" t="n"/>
       <c r="H58" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I58" s="11" t="n">
+      <c r="I58" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="J58" s="12" t="inlineStr">
-        <is>
-          <t>GENISLIGI TEYIT ET</t>
-        </is>
-      </c>
+      <c r="J58" s="5" t="inlineStr"/>
       <c r="K58" s="5" t="inlineStr">
         <is>
           <t>tam eternity</t>
@@ -4124,7 +4087,7 @@
         <v/>
       </c>
       <c r="S58" s="10" t="n">
-        <v>1.48</v>
+        <v>3.06</v>
       </c>
       <c r="T58" s="3" t="inlineStr">
         <is>
@@ -4154,21 +4117,17 @@
           <t>band</t>
         </is>
       </c>
-      <c r="F59" s="11" t="n">
-        <v>1.5</v>
+      <c r="F59" s="3" t="n">
+        <v>1.3</v>
       </c>
       <c r="G59" s="3" t="n"/>
       <c r="H59" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I59" s="11" t="n">
+      <c r="I59" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="J59" s="12" t="inlineStr">
-        <is>
-          <t>GENISLIGI TEYIT ET</t>
-        </is>
-      </c>
+      <c r="J59" s="5" t="inlineStr"/>
       <c r="K59" s="5" t="inlineStr">
         <is>
           <t>tekil/aksan tas</t>
@@ -4188,7 +4147,7 @@
         <v/>
       </c>
       <c r="S59" s="10" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="T59" s="3" t="inlineStr">
         <is>
@@ -5960,21 +5919,17 @@
           <t>band</t>
         </is>
       </c>
-      <c r="F89" s="11" t="n">
-        <v>1.5</v>
+      <c r="F89" s="3" t="n">
+        <v>6.5</v>
       </c>
       <c r="G89" s="3" t="n"/>
       <c r="H89" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I89" s="11" t="n">
+      <c r="I89" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="J89" s="12" t="inlineStr">
-        <is>
-          <t>GENISLIGI TEYIT ET</t>
-        </is>
-      </c>
+      <c r="J89" s="5" t="inlineStr"/>
       <c r="K89" s="5" t="inlineStr">
         <is>
           <t>yok / none</t>
@@ -5994,7 +5949,7 @@
         <v/>
       </c>
       <c r="S89" s="10" t="n">
-        <v>1.48</v>
+        <v>6.43</v>
       </c>
       <c r="T89" s="3" t="inlineStr">
         <is>
@@ -6299,21 +6254,21 @@
       </c>
     </row>
     <row r="96">
-      <c r="C96" s="13" t="inlineStr">
-        <is>
-          <t>SARI hucreler uretici tarafindan doldurulacak. KIRMIZI 'KONTROL' satirlarinda aciklama ile baslik farkli mm veriyor - genislik teyit edilmeli.</t>
+      <c r="C96" s="11" t="inlineStr">
+        <is>
+          <t>SARI hucreler uretici tarafindan doldurulacak. Genislikler canli Etsy aciklamalariyla teyit edildi (2026-09-08); acik celiski kalmadi.</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="C97" s="14" t="inlineStr">
+      <c r="C97" s="12" t="inlineStr">
         <is>
           <t>Gram, 14K / US 7 referansinda istenir. Diger karat ve bedenler bu referanstan panelde olceklenir.</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="C98" s="14" t="inlineStr">
+      <c r="C98" s="12" t="inlineStr">
         <is>
           <t>Kaynak: olculer Etsy urun aciklamalarindan otomatik cikarildi (Ophir Gold USA, panel DB, 93 kayit, 2026-08-28).</t>
         </is>
@@ -6340,130 +6295,130 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Varsayimlar / Assumptions</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Girdi</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Deger</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Kaynak / not</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>10K altin alis (USD/gram)</t>
         </is>
       </c>
-      <c r="B4" s="19" t="n">
+      <c r="B4" s="17" t="n">
         <v>65</v>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Panel &gt; Ayarlar &gt; Altin (gold_settings.purchase_price_10k_cents=6500)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>14K altin alis (USD/gram)</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
+      <c r="B5" s="17" t="n">
         <v>101</v>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Panel &gt; Ayarlar &gt; Altin (gold_settings.purchase_price_14k_cents=10100)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>18K altin alis (USD/gram)</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
+      <c r="B6" s="17" t="n">
         <v>130</v>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>VARSAYIM - panelde 18K kaydi YOK. 14K'nin saflik oraniyla turetildi: 101/0.583*0.750.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Fire / kayip orani</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="18" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>EON v4 motoru (lib/pricing/gold-index.ts, V4.fire). Uretici kendi firesini veriyorsa onu kullanin.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Referans beden</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>US 7</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Gram talebi bu bedende. Panel diger bedenlere olcekler.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Referans kalinlik (mm)</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="B9" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>93 listingin 63'unde aciklamada yazili; gozlenen araligin tamami 1.50-1.60 mm.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Metal maliyeti = gram x 14K alis x (1 + fire).  Toplam maliyet = metal + iscilik + tas/mihlama + dokum/diger.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>SATIS fiyati bu sayfada YOK - once gercek maliyet toplanir, fiyat sonra panelde kurulur.</t>
         </is>
@@ -6492,178 +6447,178 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Nasil doldurulur / How to fill</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Amac</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>93 listing icin GERCEK maliyet girdilerini ureticiden almak. Panelde su an gram YOK; tum listingler tek tip 366 USD fiyatta.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Doldurulacak alanlar</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>Yalnizca SARI hucreler: GRAM 14K (US 7), ISCILIK USD, TAS+MIHLAMA USD, DOKUM+DIGER USD, URETICI NOTU.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Gram</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>14 ayar ve US 7 beden icin parca basi net gram. Tek referans yeter; diger karat/bedenler panelde hesaplanir.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Iscilik</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Parca basi iscilik (USD). Tas mihlama HARIC - o ayri sutunda.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Tas + mihlama</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>Tas bedeli + mihlama iscilligi toplami (USD). Tas yoksa 0 yazin.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Dokum + diger</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>Dokum, cila, kaplama vb. varsa (USD). Yoksa 0.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>KONTROL sutunu</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>Kirmizi isaretli 9 satirda urun aciklamasi ile baslik FARKLI mm veriyor. Bu satirlarda dogru genisligi teyit edip nota yazin.</t>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>Bos. Onceki surumde 9 satir isaretliydi; 2026-09-08 denetiminde hepsi YANLIS ALARM cikti - 8 satirda kalinlik genislik sutununa yazilmisti (duzeltildi), 1 satirda basliktaki mm tas olcusuydu.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Hesaplanan sutunlar</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>'Metal maliyeti' ve 'TOPLAM MALIYET' otomatik hesaplanir - elle doldurmayin.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Bizim gram tahminimiz</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>Sadece BUYUKLUK FIKRI icin. Olcuden hesaplanan kaba tahmindir, dogrulanmis degildir - referans almayin.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>ORNEK SATIR (beklenen format)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>Urun</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>GRAM 14K (US 7)</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>ISCILIK USD</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>TAS+MIHLAMA USD</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>DOKUM+DIGER USD</t>
         </is>
       </c>
-      <c r="F14" s="25" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>URETICI NOTU</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>2mm Smooth Gold Band Ring</t>
         </is>
       </c>
-      <c r="B15" s="27" t="n">
+      <c r="B15" s="25" t="n">
         <v>2.05</v>
       </c>
-      <c r="C15" s="28" t="n">
+      <c r="C15" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="D15" s="28" t="n">
+      <c r="D15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="28" t="n">
+      <c r="E15" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="F15" s="26" t="inlineStr">
+      <c r="F15" s="24" t="inlineStr">
         <is>
           <t>Duz band, tassiz. US7 net gram.</t>
         </is>
